--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N113_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N113_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.79231841460206</v>
+        <v>2.403751742372834</v>
       </c>
       <c r="D2" t="n">
-        <v>13.72742410754844</v>
+        <v>2.230706417476621</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F2" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.50055126796085</v>
+        <v>2.031339581043639</v>
       </c>
       <c r="D3" t="n">
-        <v>11.84027654914912</v>
+        <v>1.924044939236732</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F3" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.36414788868703</v>
+        <v>2.659174031911643</v>
       </c>
       <c r="D4" t="n">
-        <v>8.217717122907899</v>
+        <v>1.335379032472534</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F4" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.74940175051052</v>
+        <v>7.75927778445796</v>
       </c>
       <c r="D5" t="n">
-        <v>44.95261508862176</v>
+        <v>7.304799951901036</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F5" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.83889112458269</v>
+        <v>5.986319807744688</v>
       </c>
       <c r="D6" t="n">
-        <v>31.61467386050004</v>
+        <v>5.137384502331257</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F6" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.44148163286885</v>
+        <v>2.834240765341188</v>
       </c>
       <c r="D7" t="n">
-        <v>18.42904088405296</v>
+        <v>2.994719143658605</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F7" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.72098922603183</v>
+        <v>5.642160749230173</v>
       </c>
       <c r="D8" t="n">
-        <v>33.77193474519736</v>
+        <v>5.48793939609457</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F8" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.42084100193615</v>
+        <v>4.618386662814624</v>
       </c>
       <c r="D9" t="n">
-        <v>29.4572141157337</v>
+        <v>4.786797293806726</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F9" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.77394932177435</v>
+        <v>4.838266764788331</v>
       </c>
       <c r="D10" t="n">
-        <v>28.90704776746944</v>
+        <v>4.697395262213784</v>
       </c>
       <c r="E10" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F10" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.73909010655336</v>
+        <v>2.88260214231492</v>
       </c>
       <c r="D11" t="n">
-        <v>17.31998067123495</v>
+        <v>2.81449685907568</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F11" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.28693806979258</v>
+        <v>1.996627436341294</v>
       </c>
       <c r="D12" t="n">
-        <v>12.89287618318184</v>
+        <v>2.09509237976705</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F12" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.16475463110562</v>
+        <v>5.551772627554664</v>
       </c>
       <c r="D13" t="n">
-        <v>34.82249355495378</v>
+        <v>5.65865520267999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F13" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.49962864240524</v>
+        <v>6.743689654390852</v>
       </c>
       <c r="D14" t="n">
-        <v>42.388989037632</v>
+        <v>6.8882107186152</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5050761589088</v>
+        <v>1.86957487582268</v>
       </c>
       <c r="F14" t="n">
-        <v>11.70987537060357</v>
+        <v>1.90285474772308</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
